--- a/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est dans le salon. Maman pose un panier. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. Noé touche la pomme. Elle est lisse. Maman dit : on nomme. On classe. Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La banane, c'est un fruit. Noé les met ensemble. La chaussette, c'est un habit. Le bonnet, c'est un habit. Noé les met ensemble. Maman dit : fruits, c'est une catégorie. Habits, c'est une catégorie. Noé répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
+          <t>Noé est dans le salon. Maman pose un panier. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. Noé touche la pomme. Elle est lisse. On nomme. On classe. Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La banane, c'est un fruit. Noé les met ensemble. La chaussette, c'est un habit. Le bonnet, c'est un habit. Noé les met ensemble. Fruits, c'est une catégorie. Habits, c'est une catégorie. Noé répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est dans le salon. Maman pose un panier. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. Noé touche la pomme. Elle est lisse.
+maman|On nomme. On classe.
+narrateur|Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La banane, c'est un fruit. Noé les met ensemble. La chaussette, c'est un habit. Le bonnet, c'est un habit. Noé les met ensemble.
+maman|Fruits, c'est une catégorie. Habits, c'est une catégorie.
+narrateur|Noé répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noé range pomme et chaussette. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noé croque la pomme. Maman plie le bonnet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Noé répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Noé range pomme et chaussette. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Noé a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Noé croque la pomme. Maman plie le bonnet.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Noé range fruits et habits</t>
+          <t>Le radiateur et le cabas de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une chaussette tiède glisse du radiateur. Le cabas s'est mélangé sur le tapis. Nino nomme et met fruits et habits chacun ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est dans le salon. Maman pose un panier. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. Noé touche la pomme. Elle est lisse. On nomme. On classe. Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La banane, c'est un fruit. Noé les met ensemble. La chaussette, c'est un habit. Le bonnet, c'est un habit. Noé les met ensemble. Fruits, c'est une catégorie. Habits, c'est une catégorie. Noé répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
+          <t>Le radiateur fait tic-tic, tout doux. Une chaussette laineuse a glissé par terre. Elle est grise, un peu chaude. Ça sent le pain chaud, depuis la cuisine. La fenêtre est un peu embuée. Dehors, la rue brille, toute mouillée. Le doudou attend sur le canapé. Il a une oreille pliée. Nino, tu vois le carré de soleil ? Il est sur le tapis rouge. Oui, maman. Il est tout chaud. Le cabas s'est un peu mélangé. Viens, on range ensemble. En ce moment, Nino s'assoit sur le tapis. Le tapis est doux sous les genoux. Maman pose le cabas près de lui. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. La pomme est lisse, maman. Touche-la. Elle est froide, un peu. Nino pose la pomme contre sa joue. La pomme sent le sucré. Et ça ? C'est le bonnet. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Nino prend la pomme rouge. Pomme. C'est un fruit. Oui. Mets-la dans le panier. Nino met la pomme dans le panier. Il prend la banane jaune. La peau est un peu collante. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Nino met la banane avec la pomme. Il prend la chaussette grise. Elle est tiède et douce. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Nino pose la chaussette sur la chaise. Il prend le bonnet rouge. Le bonnet est en laine douce. Bonnet. C'est un habit. Les habits ensemble. C'est une catégorie. Nino pose le bonnet sur la chaise. Catégorie. Fruits. Habits. Bravo, Nino. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Le panier a les fruits. La chaise a les habits. Tu as fini de ranger le cabas ? Oui, maman. Le radiateur fait encore tic-tic. Le doudou reste sur le canapé. Papa arrive avec le pain chaud. Ça sent bon, hein ? Tu as rangé tout ça ? Oui, papa. Fruits ici. Habits là. Bravo. Chaque chose a sa place.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,87 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé est dans le salon. Maman pose un panier. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. Noé touche la pomme. Elle est lisse.
-maman|On nomme. On classe.
-narrateur|Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La banane, c'est un fruit. Noé les met ensemble. La chaussette, c'est un habit. Le bonnet, c'est un habit. Noé les met ensemble.
-maman|Fruits, c'est une catégorie. Habits, c'est une catégorie.
-narrateur|Noé répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
+          <t>narrateur|Le radiateur fait tic-tic, tout doux.
+narrateur|Une chaussette laineuse a glissé par terre.
+narrateur|Elle est grise, un peu chaude.
+narrateur|Ça sent le pain chaud, depuis la cuisine.
+narrateur|La fenêtre est un peu embuée.
+narrateur|Dehors, la rue brille, toute mouillée.
+narrateur|Le doudou attend sur le canapé.
+narrateur|Il a une oreille pliée.
+maman|Nino, tu vois le carré de soleil ?
+maman|Il est sur le tapis rouge.
+enfant-m|Oui, maman.
+enfant-m|Il est tout chaud.
+maman|Le cabas s'est un peu mélangé.
+maman|Viens, on range ensemble.
+narrateur|En ce moment, Nino s'assoit sur le tapis.
+narrateur|Le tapis est doux sous les genoux.
+narrateur|Maman pose le cabas près de lui.
+narrateur|Dedans, il y a une pomme.
+narrateur|Une banane.
+narrateur|Une chaussette.
+narrateur|Un bonnet.
+enfant-m|La pomme est lisse, maman.
+maman|Touche-la.
+maman|Elle est froide, un peu.
+narrateur|Nino pose la pomme contre sa joue.
+narrateur|La pomme sent le sucré.
+enfant-m|Et ça ?
+enfant-m|C'est le bonnet.
+maman|On nomme.
+maman|On classe.
+maman|Les fruits ensemble.
+maman|Les habits ensemble.
+narrateur|Nino prend la pomme rouge.
+enfant-m|Pomme.
+enfant-m|C'est un fruit.
+maman|Oui.
+maman|Mets-la dans le panier.
+narrateur|Nino met la pomme dans le panier.
+narrateur|Il prend la banane jaune.
+narrateur|La peau est un peu collante.
+enfant-m|Banane.
+enfant-m|C'est un fruit aussi.
+maman|Les fruits ensemble.
+maman|C'est une catégorie.
+narrateur|Nino met la banane avec la pomme.
+narrateur|Il prend la chaussette grise.
+narrateur|Elle est tiède et douce.
+enfant-m|Chaussette.
+enfant-m|C'est un habit.
+maman|Oui.
+maman|Pose-la sur la chaise.
+narrateur|Nino pose la chaussette sur la chaise.
+narrateur|Il prend le bonnet rouge.
+narrateur|Le bonnet est en laine douce.
+enfant-m|Bonnet.
+enfant-m|C'est un habit.
+maman|Les habits ensemble.
+maman|C'est une catégorie.
+narrateur|Nino pose le bonnet sur la chaise.
+enfant-m|Catégorie.
+enfant-m|Fruits.
+enfant-m|Habits.
+maman|Bravo, Nino.
+maman|Tu as nommé.
+maman|Tu as classé.
+maman|Tu as mis ensemble.
+maman|C'est du bon travail.
+narrateur|Le panier a les fruits.
+narrateur|La chaise a les habits.
+maman|Tu as fini de ranger le cabas ?
+enfant-m|Oui, maman.
+narrateur|Le radiateur fait encore tic-tic.
+narrateur|Le doudou reste sur le canapé.
+narrateur|Papa arrive avec le pain chaud.
+papa|Ça sent bon, hein ?
+papa|Tu as rangé tout ça ?
+enfant-m|Oui, papa.
+enfant-m|Fruits ici.
+enfant-m|Habits là.
+papa|Bravo.
+papa|Chaque chose a sa place.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1432,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé range pomme et chaussette. Que fait-il ?</t>
+          <t>Nino range pomme et chaussette. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1588,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé range pomme et chaussette. Que fait-il ?</t>
+          <t>narrateur|Nino range pomme et chaussette.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1617,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+          <t>Nino a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Nino. C'est du bon travail. Tu as fini le panier ? Oui, papa. Les fruits sont ensemble. Et les habits ? Ensemble, sur la chaise. Le tapis rouge est un peu vide, maintenant. Le carré de soleil a bougé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1761,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+          <t>narrateur|Nino a nommé.
+narrateur|Il a classé.
+narrateur|Une catégorie pour les fruits.
+narrateur|Une catégorie pour les habits.
+maman|Tu as mis ensemble.
+maman|Bravo, Nino.
+papa|C'est du bon travail.
+papa|Tu as fini le panier ?
+enfant-m|Oui, papa.
+enfant-m|Les fruits sont ensemble.
+maman|Et les habits ?
+enfant-m|Ensemble, sur la chaise.
+narrateur|Le tapis rouge est un peu vide, maintenant.
+narrateur|Le carré de soleil a bougé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1802,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé croque la pomme. Maman plie le bonnet.</t>
+          <t>Nino croque la pomme. Elle craque, tout fort. Le jus est froid et sucré. Tu aimes ? Oui. Elle est sucrée. Maman plie le bonnet rouge. Elle pose la chaussette près du radiateur. Elle va sécher, tout doux. On coupe le pain ? Oui, papa. Le pain est encore tiède. Ça sent le matin, même l'après-midi. Tu as classé, puis tu croques. Le doudou a toujours l'oreille pliée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1938,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé croque la pomme. Maman plie le bonnet.</t>
+          <t>narrateur|Nino croque la pomme.
+narrateur|Elle craque, tout fort.
+narrateur|Le jus est froid et sucré.
+maman|Tu aimes ?
+enfant-m|Oui.
+enfant-m|Elle est sucrée.
+narrateur|Maman plie le bonnet rouge.
+narrateur|Elle pose la chaussette près du radiateur.
+maman|Elle va sécher, tout doux.
+papa|On coupe le pain ?
+enfant-m|Oui, papa.
+narrateur|Le pain est encore tiède.
+narrateur|Ça sent le matin, même l'après-midi.
+maman|Tu as classé, puis tu croques.
+narrateur|Le doudou a toujours l'oreille pliée.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1980,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Tu as fait du bon travail. Fruits ensemble. Habits ensemble. Le radiateur fait tic-tic, plus loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2120,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai nommé.
+enfant-m|J'ai classé.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Fruits ensemble.
+papa|Habits ensemble.
+narrateur|Le radiateur fait tic-tic, plus loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2187,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur fait tic-tic, tout doux. Une chaussette laineuse a glissé par terre. Elle est grise, un peu chaude. Ça sent le pain chaud, depuis la cuisine. La fenêtre est un peu embuée. Dehors, la rue brille, toute mouillée. Le doudou attend sur le canapé. Il a une oreille pliée. Nino, tu vois le carré de soleil ? Il est sur le tapis rouge. Oui, maman. Il est tout chaud. Le cabas s'est un peu mélangé. Viens, on range ensemble. En ce moment, Nino s'assoit sur le tapis. Le tapis est doux sous les genoux. Maman pose le cabas près de lui. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. La pomme est lisse, maman. Touche-la. Elle est froide, un peu. Nino pose la pomme contre sa joue. La pomme sent le sucré. Et ça ? C'est le bonnet. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Nino prend la pomme rouge. Pomme. C'est un fruit. Oui. Mets-la dans le panier. Nino met la pomme dans le panier. Il prend la banane jaune. La peau est un peu collante. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Nino met la banane avec la pomme. Il prend la chaussette grise. Elle est tiède et douce. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Nino pose la chaussette sur la chaise. Il prend le bonnet rouge. Le bonnet est en laine douce. Bonnet. C'est un habit. Les habits ensemble. C'est une catégorie. Nino pose le bonnet sur la chaise. Catégorie. Fruits. Habits. Bravo, Nino. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Le panier a les fruits. La chaise a les habits. Tu as fini de ranger le cabas ? Oui, maman. Le radiateur fait encore tic-tic. Le doudou reste sur le canapé. Papa arrive avec le pain chaud. Ça sent bon, hein ? Tu as rangé tout ça ? Oui, papa. Fruits ici. Habits là. Bravo. Chaque chose a sa place.</t>
+          <t>Le radiateur fait tic-tic, tout doux. Une chaussette laineuse a glissé par terre. Elle est grise, un peu chaude. Ça sent le pain chaud, depuis la cuisine. La fenêtre est un peu embuée. Dehors, la rue brille, toute mouillée. Le doudou attend sur le canapé. Il a une oreille pliée. Nino, tu vois le carré de soleil ? Il est sur le tapis rouge. Oui, maman. Il est tout chaud. Le cabas s'est un peu mélangé. Viens, on range ensemble. En ce moment, Nino s'assoit sur le tapis. Le tapis est doux sous les genoux. Maman pose le cabas près de lui. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. La pomme est lisse, maman. Touche-la. Elle est froide, un peu. Nino pose la pomme contre sa joue. La pomme sent le sucré. Et ça ? C'est le bonnet. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Nino prend la pomme rouge. Pomme. C'est un fruit. Oui. Mets-la dans le panier. Nino met la pomme dans le panier. Il prend la banane jaune. La peau est un peu collante. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Nino met la banane avec la pomme. Il prend la chaussette grise. Elle est tiède et douce. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Nino pose la chaussette sur la chaise. Il prend le bonnet rouge. Le bonnet est en laine douce. Bonnet. C'est un habit. Les habits ensemble. C'est une catégorie. Nino pose le bonnet sur la chaise. Catégorie. Fruits. Habits. Bravo, Nino. Tu as nommé. Tu as classé. Tu as mis ensemble. Le panier a les fruits. La chaise a les habits. Tu as fini de ranger le cabas ? Oui, maman. Le radiateur fait encore tic-tic. Le doudou reste sur le canapé. Papa arrive avec le pain chaud. Ça sent bon, hein ? Tu as rangé tout ça ? Oui, papa. Fruits ici. Habits là. Bravo. Chaque chose a sa place.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé est dans le salon. Maman pose un panier. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. Noé touche la pomme. Elle est lisse. Maman dit : on nomme. On classe. Les fruits ensemble. Les habits ensemble. La pomme, c'est un fruit. La banane, c'est un fruit. Noé les met ensemble. La chaussette, c'est un habit. Le bonnet, c'est un habit. Noé les met ensemble. Maman dit : fruits, c'est une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt;. Habits, c'est une catégorie. Noé répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le radiateur fait tic-tic, tout doux. Une chaussette laineuse a glissé par terre. Elle est grise, un peu chaude. Ça sent le pain chaud, depuis la cuisine. La fenêtre est un peu embuée. Dehors, la rue brille, toute mouillée. Le doudou attend sur le canapé. Il a une oreille pliée. Nino, tu vois le carré de soleil ? Il est sur le tapis rouge. Oui, maman. Il est tout chaud. Le cabas s'est un peu mélangé. Viens, on range ensemble. En ce moment, Nino s'assoit sur le tapis. Le tapis est doux sous les genoux. Maman pose le cabas près de lui. Dedans, il y a une pomme. Une banane. Une chaussette. Un bonnet. La pomme est lisse, maman. Touche-la. Elle est froide, un peu. Nino pose la pomme contre sa joue. La pomme sent le sucré. Et ça ? C'est le bonnet. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Nino prend la pomme rouge. Pomme. C'est un fruit. Oui. Mets-la dans le panier. Nino met la pomme dans le panier. Il prend la banane jaune. La peau est un peu collante. Banane. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Nino met la banane avec la pomme. Il prend la chaussette grise. Elle est tiède et douce. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Nino pose la chaussette sur la chaise. Il prend le bonnet rouge. Le bonnet est en laine douce. Bonnet. C'est un habit. Les habits ensemble. C'est une catégorie. Nino pose le bonnet sur la chaise. Catégorie. Fruits. Habits. Bravo, Nino. Tu as nommé. Tu as classé. Tu as mis ensemble. Le panier a les fruits. La chaise a les habits. Tu as fini de ranger le cabas ? Oui, maman. Le radiateur fait encore tic-tic. Le doudou reste sur le canapé. Papa arrive avec le pain chaud. Ça sent bon, hein ? Tu as rangé tout ça ? Oui, papa. Fruits ici. Habits là. Bravo. Chaque chose a sa place.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1390,7 +1390,6 @@
 maman|Tu as nommé.
 maman|Tu as classé.
 maman|Tu as mis ensemble.
-maman|C'est du bon travail.
 narrateur|Le panier a les fruits.
 narrateur|La chaise a les habits.
 maman|Tu as fini de ranger le cabas ?
@@ -1407,7 +1406,6 @@
 papa|Chaque chose a sa place.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1437,7 +1435,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé range pomme et chaussette. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino range pomme et chaussette. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1592,7 +1590,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1617,12 +1614,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Nino. C'est du bon travail. Tu as fini le panier ? Oui, papa. Les fruits sont ensemble. Et les habits ? Ensemble, sur la chaise. Le tapis rouge est un peu vide, maintenant. Le carré de soleil a bougé.</t>
+          <t>Nino a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Nino. Tu as fini le panier ? Oui, papa. Les fruits sont ensemble. Et les habits ? Ensemble, sur la chaise. Le tapis rouge est un peu vide, maintenant. Le carré de soleil a bougé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé a nommé. Il a classé. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les habits.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Nino. Tu as fini le panier ? Oui, papa. Les fruits sont ensemble. Et les habits ? Ensemble, sur la chaise. Le tapis rouge est un peu vide, maintenant. Le carré de soleil a bougé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1767,7 +1764,6 @@
 narrateur|Une catégorie pour les habits.
 maman|Tu as mis ensemble.
 maman|Bravo, Nino.
-papa|C'est du bon travail.
 papa|Tu as fini le panier ?
 enfant-m|Oui, papa.
 enfant-m|Les fruits sont ensemble.
@@ -1777,7 +1773,6 @@
 narrateur|Le carré de soleil a bougé.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,7 +1802,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé croque la pomme. Maman plie le bonnet.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino croque la pomme. Elle craque, tout fort. Le jus est froid et sucré. Tu aimes ? Oui. Elle est sucrée. Maman plie le bonnet rouge. Elle pose la chaussette près du radiateur. Elle va sécher, tout doux. On coupe le pain ? Oui, papa. Le pain est encore tiède. Ça sent le matin, même l'après-midi. Tu as classé, puis tu croques. Le doudou a toujours l'oreille pliée.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1955,7 +1950,6 @@
 narrateur|Le doudou a toujours l'oreille pliée.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1980,12 +1974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai nommé. J'ai classé. Bravo. Tu as fait du bon travail. Fruits ensemble. Habits ensemble. Le radiateur fait tic-tic, plus loin. L'histoire est finie.</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Fruits ensemble. Habits ensemble. Le radiateur fait tic-tic, plus loin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Fruits ensemble. Habits ensemble. Le radiateur fait tic-tic, plus loin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2123,14 +2117,11 @@
           <t>enfant-m|J'ai nommé.
 enfant-m|J'ai classé.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 papa|Fruits ensemble.
 papa|Habits ensemble.
-narrateur|Le radiateur fait tic-tic, plus loin.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le radiateur fait tic-tic, plus loin.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2149,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2194,6 +2185,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noé, maman</t>
+          <t>Nino, maman, papa</t>
         </is>
       </c>
     </row>
